--- a/SHINHWA_QMS_WORKFLOW/99_산출물/발송용_최종_20261008/00_발송체크리스트.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/99_산출물/발송용_최종_20261008/00_발송체크리스트.xlsx
@@ -565,6 +565,16 @@
           <t>첨부_지성규_확인요청표.xlsx</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>인편(출력물 직접 전달)</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -605,6 +615,16 @@
           <t>첨부_이광재_확인요청표.xlsx</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>인편(출력물 직접 전달)</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -645,6 +665,16 @@
           <t>첨부_김명용_확인요청표.xlsx</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>인편(출력물 직접 전달)</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -685,6 +715,16 @@
           <t>첨부_이은주_확인요청표.xlsx</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>인편(출력물 직접 전달)</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -725,6 +765,16 @@
           <t>첨부_황지환_확인요청표.xlsx</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>인편(출력물 직접 전달)</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -765,6 +815,16 @@
           <t>첨부_한상돈_확인요청표.xlsx</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>인편(출력물 직접 전달)</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -805,6 +865,16 @@
           <t>첨부_김주태_확인요청표.xlsx</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>인편(출력물 직접 전달)</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -845,6 +915,16 @@
           <t>첨부_박철호_확인요청표.xlsx</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>인편(출력물 직접 전달)</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -885,6 +965,16 @@
           <t>첨부_김운주_확인요청표.xlsx</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>인편(출력물 직접 전달)</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -925,6 +1015,16 @@
           <t>첨부_안종명_확인요청표.xlsx</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>인편(출력물 직접 전달)</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -965,15 +1065,23 @@
           <t>첨부_이은주_박철호공동_확인요청표.xlsx</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>인편(출력물 직접 전달)</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
         <v>235</v>
       </c>

--- a/SHINHWA_QMS_WORKFLOW/99_산출물/발송용_최종_20261008/00_발송체크리스트.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/99_산출물/발송용_최종_20261008/00_발송체크리스트.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -497,30 +497,25 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>수신처(입력)</t>
+          <t>발송 방법(입력)</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>발송 방법(입력)</t>
+          <t>발송일(입력)</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>발송일(입력)</t>
+          <t>발송자(입력)</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>발송자(입력)</t>
+          <t>회신일(입력)</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>회신일(입력)</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>회신 상태(입력)</t>
         </is>
@@ -565,12 +560,12 @@
           <t>첨부_지성규_확인요청표.xlsx</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>인편(출력물 직접 전달)</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
-        <is>
-          <t>인편(출력물 직접 전달)</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
@@ -615,12 +610,12 @@
           <t>첨부_이광재_확인요청표.xlsx</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>인편(출력물 직접 전달)</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
-        <is>
-          <t>인편(출력물 직접 전달)</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
@@ -665,12 +660,12 @@
           <t>첨부_김명용_확인요청표.xlsx</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>인편(출력물 직접 전달)</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
-        <is>
-          <t>인편(출력물 직접 전달)</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
@@ -715,12 +710,12 @@
           <t>첨부_이은주_확인요청표.xlsx</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>인편(출력물 직접 전달)</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
-        <is>
-          <t>인편(출력물 직접 전달)</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
@@ -765,12 +760,12 @@
           <t>첨부_황지환_확인요청표.xlsx</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>인편(출력물 직접 전달)</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
-        <is>
-          <t>인편(출력물 직접 전달)</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
@@ -815,12 +810,12 @@
           <t>첨부_한상돈_확인요청표.xlsx</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>인편(출력물 직접 전달)</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
-        <is>
-          <t>인편(출력물 직접 전달)</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
@@ -865,12 +860,12 @@
           <t>첨부_김주태_확인요청표.xlsx</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>인편(출력물 직접 전달)</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
-        <is>
-          <t>인편(출력물 직접 전달)</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
@@ -915,12 +910,12 @@
           <t>첨부_박철호_확인요청표.xlsx</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>인편(출력물 직접 전달)</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
-        <is>
-          <t>인편(출력물 직접 전달)</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
@@ -965,12 +960,12 @@
           <t>첨부_김운주_확인요청표.xlsx</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>인편(출력물 직접 전달)</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
-        <is>
-          <t>인편(출력물 직접 전달)</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
@@ -1015,12 +1010,12 @@
           <t>첨부_안종명_확인요청표.xlsx</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>인편(출력물 직접 전달)</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
-        <is>
-          <t>인편(출력물 직접 전달)</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
@@ -1065,12 +1060,12 @@
           <t>첨부_이은주_박철호공동_확인요청표.xlsx</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>인편(출력물 직접 전달)</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
-        <is>
-          <t>인편(출력물 직접 전달)</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
